--- a/hardware/SYP Projekt Money Managment.xlsx
+++ b/hardware/SYP Projekt Money Managment.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11027"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/moritz/Documents/GitHub/HulaSwirl/hardware/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://htblaleonding-my.sharepoint.com/personal/l_oberndorfer_htblaleonding_onmicrosoft_com/Documents/HTL - JG4/SYP/HulaSwirl/hardware/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7EA2172E-0AC4-0140-8292-6197BD1A5B32}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="13_ncr:1_{7EA2172E-0AC4-0140-8292-6197BD1A5B32}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B2AEF512-7283-45BA-BDBA-756897DAEE69}"/>
   <bookViews>
-    <workbookView xWindow="140" yWindow="1040" windowWidth="20340" windowHeight="24160" xr2:uid="{5C2BC352-EA72-3047-A569-738E49AE4B2F}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{5C2BC352-EA72-3047-A569-738E49AE4B2F}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -213,8 +213,8 @@
     <xf numFmtId="164" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Link" xfId="1" builtinId="8"/>
+    <cellStyle name="Standard" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -230,7 +230,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -547,23 +547,23 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4F860369-660E-9242-9C25-0ADA69D6C52D}">
   <dimension ref="A1:G23"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15" customWidth="1"/>
-    <col min="2" max="2" width="40.33203125" customWidth="1"/>
+    <col min="2" max="2" width="40.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>1</v>
       </c>
@@ -586,7 +586,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>7</v>
       </c>
@@ -612,7 +612,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:7" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>8</v>
       </c>
@@ -638,7 +638,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:7" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>14</v>
       </c>
@@ -648,7 +648,7 @@
       <c r="E9" s="4"/>
       <c r="F9" s="4"/>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>15</v>
       </c>
@@ -674,7 +674,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>18</v>
       </c>
@@ -700,7 +700,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>19</v>
       </c>
@@ -726,7 +726,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>20</v>
       </c>
@@ -752,7 +752,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
         <v>23</v>
       </c>
@@ -779,7 +779,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
         <v>25</v>
       </c>
@@ -788,7 +788,7 @@
       <c r="E15" s="4"/>
       <c r="F15" s="4"/>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
         <v>26</v>
       </c>
@@ -814,7 +814,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>11</v>
       </c>
@@ -835,7 +835,7 @@
         <v>32.393333333333331</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>31</v>
       </c>
@@ -844,7 +844,7 @@
         <v>101.03</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>27</v>
       </c>
@@ -853,7 +853,7 @@
         <v>28.97</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="C23" s="4"/>
       <c r="D23" s="4"/>
       <c r="E23" s="4"/>
@@ -866,6 +866,7 @@
     <hyperlink ref="B11" r:id="rId3" display="https://www.amazon.de/-/en/Silicone-Electric-Stranded-Electrical-Applications/dp/B0C7QTH8TC?crid=1KOPOHRL7HRBO&amp;dib=eyJ2IjoiMSJ9.VN-g2lxkL868stgPOid0hK-Z35gETrYV7C5EdQnFRzCZPsqORFx4Z_SH0RIZNgQYu2g9FpvYaxyd_MPuPCVTQdhz6uTaWkiVfefgJlKxr4HNxHihUeOjAN50T7r3Gefnbucow4WWhrTsmZ2TixYfvY0uSpUlG7JzCKswtQBkrttnwUdIazaP57FE8hWmhzsscCl8KabjG1RCoePhFvPVkvQsKLcIAe5IiU7VmTSNhgLq85Q3f06uVFUIjoEhsyG2ioaEdXMOBR0fOzU-giWJTTrlyM35I8cGNH2FFfktH2o.yEOPCQuFURyct9ee-pa2RtkbTOGPW0ecgD_wWKWI_90&amp;dib_tag=se&amp;keywords=18%2BAWG%2Bwire&amp;qid=1730973174&amp;sprefix=18%2Bawg%2Bwir%2Caps%2C100&amp;sr=8-18&amp;th=1" xr:uid="{3CDA3DBA-5E58-CB4A-B3C2-50DC42B5ACD0}"/>
     <hyperlink ref="B12" r:id="rId4" display="https://www.amazon.de/-/en/Adapter-100-240-Transformer-Monitor-Amplifier-Power-supply-12-V-3/dp/B0BP66JZLX?crid=2L6PFKLCEVK81&amp;dib=eyJ2IjoiMSJ9._lkwspqmhU_fj9XvC2uB5Cll1bhHvjucTD1A1D93tQk0JwlyQ4i6_3KLH50N6DVbERmRfGBI-todPqX7FLL5o5m57lb4gFZdm8kdYJ72AwpwxX-6JuOLioxnVWqHmBiIfDy4Fyy2Cytbg1BVEG4vdmPcsibKb6P96-IsLemjw9XJiA0fi4SjBPL8Zhhijl2xy5fPbpkNvHEwu6iooqHzu_G1vLNEElQQjCUVDi00Y8c.mPqtxyoN5vhUvYyrQxUjrDtudTG9thY3_s2Dg8dyO-E&amp;dib_tag=se&amp;keywords=power+supply+3A&amp;qid=1731005289&amp;sprefix=power+supply+3a%2Caps%2C120&amp;sr=8-3" xr:uid="{75D88FC1-C021-B242-AEE2-8C0FD7B46613}"/>
     <hyperlink ref="B13" r:id="rId5" display="https://www.amazon.de/-/en/HUAREW-Breadboard-Dupont-Points-Arduino/dp/B0B5TCKTQH?crid=2H1V44Q263MD5&amp;dib=eyJ2IjoiMSJ9.aRQeJMI5vdGBirt5tCbbkvFrQGta46bFt4TW95QpKEI_qHNschVOZrDLg2LZDJJZQAXxyh-2uU9z9h8oMATldodApJRJ3Aw0v33jJoYkZPAIOUjT6Rn-n3cJCxTrRwhqyIvsNW9NoxCx8P_a7BCcYzp2_8deppQsQIBABuIQxDvttl7ca73gW1j-YaZYmrjlH1v6Ai5UeNeYgtCnwP9a1o27a4E_BofieoY3sTTA0scZIUI-Q_9jp4Pp4yylzZ1g0V7kDiI2c-HRnldF07111cC90ts6DsUeTzG2M4DqR58.GKKUBGBXDt9iH5LYVhwsJuKDZRnn8kGujHwg4HpLXqc&amp;dib_tag=se&amp;keywords=steckplatine&amp;qid=1730977442&amp;sprefix=steckplatine%2Caps%2C145&amp;sr=8-15" xr:uid="{1FBA583B-B7E5-6445-A245-065661D88F99}"/>
+    <hyperlink ref="B16" r:id="rId6" xr:uid="{4909FE4D-B08E-4951-A66A-923E52FFBAEF}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
